--- a/data/environmental.xlsx
+++ b/data/environmental.xlsx
@@ -469,297 +469,297 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B2" t="n">
-        <v>232.4</v>
+        <v>220.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.544</v>
+        <v>0.529</v>
       </c>
       <c r="D2" t="n">
-        <v>6261</v>
+        <v>6332</v>
       </c>
       <c r="E2" t="n">
-        <v>47903</v>
+        <v>48354</v>
       </c>
       <c r="F2" t="n">
-        <v>523543</v>
+        <v>521413</v>
       </c>
       <c r="G2" t="n">
-        <v>48</v>
+        <v>59.5</v>
       </c>
       <c r="H2" t="n">
-        <v>8.08</v>
+        <v>8.06</v>
       </c>
       <c r="I2" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B3" t="n">
-        <v>128.9</v>
+        <v>170.6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.448</v>
+        <v>0.492</v>
       </c>
       <c r="D3" t="n">
-        <v>6044</v>
+        <v>6420</v>
       </c>
       <c r="E3" t="n">
-        <v>48677</v>
+        <v>42686</v>
       </c>
       <c r="F3" t="n">
-        <v>466859</v>
+        <v>458516</v>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>41.7</v>
       </c>
       <c r="H3" t="n">
-        <v>7.34</v>
+        <v>7.95</v>
       </c>
       <c r="I3" t="n">
-        <v>34.3</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B4" t="n">
-        <v>170.3</v>
+        <v>176.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.458</v>
+        <v>0.431</v>
       </c>
       <c r="D4" t="n">
-        <v>5679</v>
+        <v>5205</v>
       </c>
       <c r="E4" t="n">
-        <v>38047</v>
+        <v>41297</v>
       </c>
       <c r="F4" t="n">
-        <v>452971</v>
+        <v>467271</v>
       </c>
       <c r="G4" t="n">
-        <v>45.8</v>
+        <v>50.1</v>
       </c>
       <c r="H4" t="n">
-        <v>7.69</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>36.1</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B5" t="n">
-        <v>126.6</v>
+        <v>174.5</v>
       </c>
       <c r="C5" t="n">
-        <v>0.455</v>
+        <v>0.36</v>
       </c>
       <c r="D5" t="n">
-        <v>5260</v>
+        <v>6689</v>
       </c>
       <c r="E5" t="n">
-        <v>51029</v>
+        <v>49063</v>
       </c>
       <c r="F5" t="n">
-        <v>530629</v>
+        <v>557503</v>
       </c>
       <c r="G5" t="n">
-        <v>29.1</v>
+        <v>27.7</v>
       </c>
       <c r="H5" t="n">
-        <v>6.75</v>
+        <v>7.98</v>
       </c>
       <c r="I5" t="n">
-        <v>34.9</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B6" t="n">
-        <v>216.8</v>
+        <v>162.9</v>
       </c>
       <c r="C6" t="n">
-        <v>0.433</v>
+        <v>0.59</v>
       </c>
       <c r="D6" t="n">
-        <v>6621</v>
+        <v>5857</v>
       </c>
       <c r="E6" t="n">
-        <v>43751</v>
+        <v>43262</v>
       </c>
       <c r="F6" t="n">
-        <v>472624</v>
+        <v>547970</v>
       </c>
       <c r="G6" t="n">
-        <v>39.5</v>
+        <v>50.3</v>
       </c>
       <c r="H6" t="n">
-        <v>7.69</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>36.1</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B7" t="n">
-        <v>129.3</v>
+        <v>154.1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.416</v>
+        <v>0.431</v>
       </c>
       <c r="D7" t="n">
-        <v>5681</v>
+        <v>5879</v>
       </c>
       <c r="E7" t="n">
-        <v>43941</v>
+        <v>44624</v>
       </c>
       <c r="F7" t="n">
-        <v>486238</v>
+        <v>460806</v>
       </c>
       <c r="G7" t="n">
-        <v>41.4</v>
+        <v>63</v>
       </c>
       <c r="H7" t="n">
-        <v>8.220000000000001</v>
+        <v>7.33</v>
       </c>
       <c r="I7" t="n">
-        <v>23.1</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B8" t="n">
-        <v>239.2</v>
+        <v>204.5</v>
       </c>
       <c r="C8" t="n">
-        <v>0.513</v>
+        <v>0.446</v>
       </c>
       <c r="D8" t="n">
-        <v>5767</v>
+        <v>5501</v>
       </c>
       <c r="E8" t="n">
-        <v>40630</v>
+        <v>39881</v>
       </c>
       <c r="F8" t="n">
-        <v>438808</v>
+        <v>524184</v>
       </c>
       <c r="G8" t="n">
-        <v>88.2</v>
+        <v>78</v>
       </c>
       <c r="H8" t="n">
-        <v>8.640000000000001</v>
+        <v>7.23</v>
       </c>
       <c r="I8" t="n">
-        <v>21.3</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B9" t="n">
-        <v>257.7</v>
+        <v>214</v>
       </c>
       <c r="C9" t="n">
-        <v>0.531</v>
+        <v>0.578</v>
       </c>
       <c r="D9" t="n">
-        <v>6551</v>
+        <v>5901</v>
       </c>
       <c r="E9" t="n">
-        <v>44135</v>
+        <v>51376</v>
       </c>
       <c r="F9" t="n">
-        <v>553761</v>
+        <v>447934</v>
       </c>
       <c r="G9" t="n">
-        <v>63</v>
+        <v>66.5</v>
       </c>
       <c r="H9" t="n">
-        <v>8.369999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="I9" t="n">
-        <v>32.5</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B10" t="n">
-        <v>244.8</v>
+        <v>189.9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.485</v>
+        <v>0.384</v>
       </c>
       <c r="D10" t="n">
-        <v>5401</v>
+        <v>5688</v>
       </c>
       <c r="E10" t="n">
-        <v>42273</v>
+        <v>48558</v>
       </c>
       <c r="F10" t="n">
-        <v>525581</v>
+        <v>538439</v>
       </c>
       <c r="G10" t="n">
-        <v>38.9</v>
+        <v>54.2</v>
       </c>
       <c r="H10" t="n">
-        <v>7.86</v>
+        <v>7.55</v>
       </c>
       <c r="I10" t="n">
-        <v>27.1</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B11" t="n">
-        <v>213.2</v>
+        <v>223.5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.55</v>
+        <v>0.464</v>
       </c>
       <c r="D11" t="n">
-        <v>5878</v>
+        <v>6133</v>
       </c>
       <c r="E11" t="n">
-        <v>46163</v>
+        <v>51823</v>
       </c>
       <c r="F11" t="n">
-        <v>558232</v>
+        <v>454300</v>
       </c>
       <c r="G11" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H11" t="n">
-        <v>6.98</v>
+        <v>7.2</v>
       </c>
       <c r="I11" t="n">
-        <v>20.7</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B12" t="n">
         <v>241.7</v>
@@ -777,7 +777,7 @@
         <v>518449</v>
       </c>
       <c r="G12" t="n">
-        <v>53</v>
+        <v>31.4</v>
       </c>
       <c r="H12" t="n">
         <v>7.15</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" t="n">
         <v>259.9</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" t="n">
         <v>193.6</v>
@@ -846,7 +846,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B15" t="n">
         <v>244.4</v>
@@ -875,7 +875,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B16" t="n">
         <v>250.1</v>
@@ -904,7 +904,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
         <v>237.3</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B18" t="n">
         <v>224</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B19" t="n">
         <v>147.1</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B20" t="n">
         <v>152.9</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B21" t="n">
         <v>193</v>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B22" t="n">
         <v>204.2</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B23" t="n">
         <v>181.7</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B24" t="n">
         <v>201.9</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B25" t="n">
         <v>123.2</v>
